--- a/artfynd/A 30892-2020 artfynd.xlsx
+++ b/artfynd/A 30892-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -5191,6 +5191,110 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114866052</v>
+      </c>
+      <c r="B39" t="n">
+        <v>82998</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Örstigsnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>621597</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6511904</v>
+      </c>
+      <c r="S39" t="n">
+        <v>100</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30892-2020 artfynd.xlsx
+++ b/artfynd/A 30892-2020 artfynd.xlsx
@@ -5196,11 +5196,11 @@
         <v>114866052</v>
       </c>
       <c r="B39" t="n">
-        <v>83054</v>
+        <v>83201</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">

--- a/artfynd/A 30892-2020 artfynd.xlsx
+++ b/artfynd/A 30892-2020 artfynd.xlsx
@@ -5196,7 +5196,7 @@
         <v>114866052</v>
       </c>
       <c r="B39" t="n">
-        <v>83201</v>
+        <v>83208</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2020 artfynd.xlsx
+++ b/artfynd/A 30892-2020 artfynd.xlsx
@@ -5196,7 +5196,7 @@
         <v>114866052</v>
       </c>
       <c r="B39" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
